--- a/data/trans_orig/P1414-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2012</t>
+          <t>Población con diagnóstico de fibromialgia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297238</t>
+          <t>298488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311279</t>
+          <t>311488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>734933</t>
+          <t>735628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748536</t>
+          <t>748638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411789</t>
+          <t>413086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328841</t>
+          <t>328065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337029</t>
+          <t>337039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>745921</t>
+          <t>745834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754898</t>
+          <t>754857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623689</t>
+          <t>624115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240319</t>
+          <t>239426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253935</t>
+          <t>253815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867908</t>
+          <t>868719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882274</t>
+          <t>882729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>21653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1152243</t>
+          <t>1151129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>745643</t>
+          <t>745901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>760374</t>
+          <t>759941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901147</t>
+          <t>1902078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917134</t>
+          <t>1917365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42167</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>45838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502952</t>
+          <t>502390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509636</t>
+          <t>509631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718079</t>
+          <t>718043</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>739484</t>
+          <t>739648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1224434</t>
+          <t>1225005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1248405</t>
+          <t>1247518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>39269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38920</t>
+          <t>39676</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1068138</t>
+          <t>1069116</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1090025</t>
+          <t>1090201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336347</t>
+          <t>1335591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356933</t>
+          <t>1356958</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>73529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112591</t>
+          <t>112613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81370</t>
+          <t>78350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119090</t>
+          <t>119938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3407232</t>
+          <t>3407484</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3418619</t>
+          <t>3418736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3433357</t>
+          <t>3433335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3474624</t>
+          <t>3472419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6848768</t>
+          <t>6847920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6886488</t>
+          <t>6889508</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2016</t>
+          <t>Población con diagnóstico de fibromialgia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419747</t>
+          <t>420056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336120</t>
+          <t>334506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344971</t>
+          <t>344950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760771</t>
+          <t>760680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772883</t>
+          <t>772960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369613</t>
+          <t>369127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359141</t>
+          <t>359514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370221</t>
+          <t>370201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732149</t>
+          <t>733770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745858</t>
+          <t>746501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513333</t>
+          <t>514034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521914</t>
+          <t>520965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153080</t>
+          <t>153361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163930</t>
+          <t>163995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671394</t>
+          <t>671587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>683989</t>
+          <t>683850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,47 +4446,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>33656</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>23374</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>2,35%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>33656</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>23107</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>46146</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138135</t>
+          <t>1138081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148544</t>
+          <t>1147658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>783411</t>
+          <t>784714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>806505</t>
+          <t>807173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,47 +4559,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1941858</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1929117</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1952140</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>97,65%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1941858</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1929368</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1952407</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>64001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67035</t>
+          <t>69213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615291</t>
+          <t>615228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>673357</t>
+          <t>674243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>700801</t>
+          <t>701360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1291915</t>
+          <t>1289737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1321291</t>
+          <t>1320241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43402</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1038623</t>
+          <t>1039182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1061750</t>
+          <t>1062486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1326364</t>
+          <t>1327111</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1348642</t>
+          <t>1349628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102378</t>
+          <t>103977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147405</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116120</t>
+          <t>117345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164103</t>
+          <t>166762</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3360912</t>
+          <t>3362276</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3378277</t>
+          <t>3378023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3384191</t>
+          <t>3382268</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3429218</t>
+          <t>3427619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6753215</t>
+          <t>6750556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6801198</t>
+          <t>6799973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2023</t>
+          <t>Población con diagnóstico de fibromialgia en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498365</t>
+          <t>498826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429214</t>
+          <t>429404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440395</t>
+          <t>440555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>932314</t>
+          <t>931734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943981</t>
+          <t>943987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447770</t>
+          <t>447857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361125</t>
+          <t>361391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372093</t>
+          <t>372403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810856</t>
+          <t>811420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822655</t>
+          <t>823114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652356</t>
+          <t>651409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666276</t>
+          <t>666595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149880</t>
+          <t>150096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160131</t>
+          <t>160116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>804800</t>
+          <t>805925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828433</t>
+          <t>828248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38775</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>39188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1026765</t>
+          <t>1026518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1033348</t>
+          <t>1033247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936350</t>
+          <t>936184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960874</t>
+          <t>962455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1970187</t>
+          <t>1970040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1988911</t>
+          <t>1989890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>28906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51099</t>
+          <t>51738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>31259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52205</t>
+          <t>51963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466195</t>
+          <t>466118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>784124</t>
+          <t>783485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>806337</t>
+          <t>806317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255224</t>
+          <t>1255466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1276071</t>
+          <t>1276170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27398</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>44958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234150</t>
+          <t>234714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>713891</t>
+          <t>714676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731273</t>
+          <t>731525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>951860</t>
+          <t>953095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>970655</t>
+          <t>971076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105983</t>
+          <t>111149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156601</t>
+          <t>158171</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123994</t>
+          <t>126487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172500</t>
+          <t>172544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3346641</t>
+          <t>3345576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3362451</t>
+          <t>3361973</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3405517</t>
+          <t>3403947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3456135</t>
+          <t>3450969</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6759859</t>
+          <t>6759815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6808365</t>
+          <t>6805872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1414-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Clase-trans_orig.xlsx
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298488</t>
+          <t>298921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311488</t>
+          <t>311197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735628</t>
+          <t>734588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748638</t>
+          <t>748585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413086</t>
+          <t>414266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328065</t>
+          <t>328166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337039</t>
+          <t>337042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>745834</t>
+          <t>744949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754857</t>
+          <t>754842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624115</t>
+          <t>624479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239426</t>
+          <t>239701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253815</t>
+          <t>253745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>868719</t>
+          <t>868190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882729</t>
+          <t>882361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1151129</t>
+          <t>1152037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>745901</t>
+          <t>745467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>759941</t>
+          <t>759902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1902078</t>
+          <t>1900142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917365</t>
+          <t>1917007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45838</t>
+          <t>46394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502390</t>
+          <t>502397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509631</t>
+          <t>509626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718043</t>
+          <t>716949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>739648</t>
+          <t>738997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1225005</t>
+          <t>1224449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1247518</t>
+          <t>1247208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1069116</t>
+          <t>1068998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1090201</t>
+          <t>1090948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1335591</t>
+          <t>1334981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356958</t>
+          <t>1356858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73529</t>
+          <t>74503</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112613</t>
+          <t>112173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>78583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119938</t>
+          <t>120244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3407484</t>
+          <t>3407043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3418736</t>
+          <t>3418758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3433335</t>
+          <t>3433775</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3472419</t>
+          <t>3471445</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6847920</t>
+          <t>6847614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6889508</t>
+          <t>6889275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420056</t>
+          <t>419228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334506</t>
+          <t>335247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344950</t>
+          <t>344965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760680</t>
+          <t>759870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772960</t>
+          <t>772475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369127</t>
+          <t>370097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359514</t>
+          <t>359100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370201</t>
+          <t>370162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733770</t>
+          <t>733329</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746501</t>
+          <t>745784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514034</t>
+          <t>513424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520965</t>
+          <t>520964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153361</t>
+          <t>153277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163995</t>
+          <t>163101</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671587</t>
+          <t>671820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>683850</t>
+          <t>683930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41162</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138081</t>
+          <t>1138977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147658</t>
+          <t>1147589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>784714</t>
+          <t>786119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>807173</t>
+          <t>806994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1929117</t>
+          <t>1928734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952140</t>
+          <t>1951873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>35594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64001</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69213</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615228</t>
+          <t>615182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>674243</t>
+          <t>675649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>701360</t>
+          <t>702650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1289737</t>
+          <t>1293271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1320241</t>
+          <t>1322504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42843</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1039182</t>
+          <t>1039102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1062486</t>
+          <t>1062307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1327111</t>
+          <t>1325874</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1349628</t>
+          <t>1348164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149328</t>
+          <t>150310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117345</t>
+          <t>115065</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166762</t>
+          <t>165482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3362276</t>
+          <t>3362426</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3378023</t>
+          <t>3378071</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3382268</t>
+          <t>3381286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3427619</t>
+          <t>3428724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6750556</t>
+          <t>6751836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6799973</t>
+          <t>6802253</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6110,27 +6110,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>503174</t>
+          <t>548309</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>498826</t>
+          <t>543962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504247</t>
+          <t>549428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>436030</t>
+          <t>475561</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429404</t>
+          <t>466908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440555</t>
+          <t>480064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,27 +6180,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>939204</t>
+          <t>1023869</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>931734</t>
+          <t>1015404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943987</t>
+          <t>1028897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504247</t>
+          <t>549428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504247</t>
+          <t>549428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504247</t>
+          <t>549428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446661</t>
+          <t>487018</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446661</t>
+          <t>487018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446661</t>
+          <t>487018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950908</t>
+          <t>1036445</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950908</t>
+          <t>1036445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950908</t>
+          <t>1036445</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6453,27 +6453,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>450544</t>
+          <t>481517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447857</t>
+          <t>479152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451631</t>
+          <t>482625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>367353</t>
+          <t>406941</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361391</t>
+          <t>399196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372403</t>
+          <t>411633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>817897</t>
+          <t>888458</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>811420</t>
+          <t>881320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823114</t>
+          <t>893687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451631</t>
+          <t>482625</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451631</t>
+          <t>482625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451631</t>
+          <t>482625</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380654</t>
+          <t>421183</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380654</t>
+          <t>421183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380654</t>
+          <t>421183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832285</t>
+          <t>903808</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832285</t>
+          <t>903808</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832285</t>
+          <t>903808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>660916</t>
+          <t>463708</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651409</t>
+          <t>454905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666595</t>
+          <t>467861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>156127</t>
+          <t>175783</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150096</t>
+          <t>169567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160116</t>
+          <t>180145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>817044</t>
+          <t>639492</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805925</t>
+          <t>630262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828248</t>
+          <t>645982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,22 +7026,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>42518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -7139,27 +7139,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1031181</t>
+          <t>1128192</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1026518</t>
+          <t>1123487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1033247</t>
+          <t>1130166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>947698</t>
+          <t>827163</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936184</t>
+          <t>818357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>962455</t>
+          <t>834106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1978878</t>
+          <t>1955356</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1970040</t>
+          <t>1945538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1989890</t>
+          <t>1963456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034103</t>
+          <t>1131032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034103</t>
+          <t>1131032</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034103</t>
+          <t>1131032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975125</t>
+          <t>857023</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975125</t>
+          <t>857023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975125</t>
+          <t>857023</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2009228</t>
+          <t>1988056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2009228</t>
+          <t>1988056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2009228</t>
+          <t>1988056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40025</t>
+          <t>45919</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51738</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>47486</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31259</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51963</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7482,27 +7482,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>470690</t>
+          <t>563430</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466118</t>
+          <t>559743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>564997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>795198</t>
+          <t>779183</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>783485</t>
+          <t>767436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>788795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1265887</t>
+          <t>1342613</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255466</t>
+          <t>1330985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1276170</t>
+          <t>1352609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>564997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>564997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>564997</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>835223</t>
+          <t>825102</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>835223</t>
+          <t>825102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>835223</t>
+          <t>825102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307429</t>
+          <t>1390099</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307429</t>
+          <t>1390099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307429</t>
+          <t>1390099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35244</t>
+          <t>39062</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -7825,27 +7825,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234714</t>
+          <t>232158</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7860,27 +7860,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>723378</t>
+          <t>801689</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>714676</t>
+          <t>791816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731525</t>
+          <t>810881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>962809</t>
+          <t>1037819</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>953095</t>
+          <t>1026515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>971076</t>
+          <t>1046452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>757546</t>
+          <t>839653</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>757546</t>
+          <t>839653</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>757546</t>
+          <t>839653</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>998053</t>
+          <t>1076881</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>998053</t>
+          <t>1076881</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>998053</t>
+          <t>1076881</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>136335</t>
+          <t>151156</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111149</t>
+          <t>134032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158171</t>
+          <t>174223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>150640</t>
+          <t>165924</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126487</t>
+          <t>145660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172544</t>
+          <t>185345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3355935</t>
+          <t>3421286</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3345576</t>
+          <t>3410354</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3361973</t>
+          <t>3427068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3425783</t>
+          <t>3466320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3403947</t>
+          <t>3443253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3450969</t>
+          <t>3483444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6781719</t>
+          <t>6887605</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6759815</t>
+          <t>6868184</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6805872</t>
+          <t>6907869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370240</t>
+          <t>3436053</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370240</t>
+          <t>3436053</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370240</t>
+          <t>3436053</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3562118</t>
+          <t>3617476</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3562118</t>
+          <t>3617476</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3562118</t>
+          <t>3617476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6932359</t>
+          <t>7053529</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6932359</t>
+          <t>7053529</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6932359</t>
+          <t>7053529</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
